--- a/Assets/Document/云熹约定项目文档/9.事件配置表/特殊事件选项数值配置表.xlsx
+++ b/Assets/Document/云熹约定项目文档/9.事件配置表/特殊事件选项数值配置表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="68">
   <si>
     <t>男主姓名</t>
   </si>
@@ -195,6 +195,42 @@
   </si>
   <si>
     <t>欣然赴约，探寻真相</t>
+  </si>
+  <si>
+    <t>何行舟</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>顺水推舟，以退为进</t>
+  </si>
+  <si>
+    <t>冷静疏离，划清界限</t>
+  </si>
+  <si>
+    <t>拒绝情绪绑架</t>
+  </si>
+  <si>
+    <t>肯定他的灵魂</t>
+  </si>
+  <si>
+    <t>解释你的行为</t>
+  </si>
+  <si>
+    <t>道歉也得还钱</t>
+  </si>
+  <si>
+    <t>主动提出他心中所想</t>
+  </si>
+  <si>
+    <t>看看他葫芦里卖的是什么药</t>
+  </si>
+  <si>
+    <t>接受他的暗示</t>
+  </si>
+  <si>
+    <t>该为自己而明</t>
   </si>
 </sst>
 </file>
@@ -1342,7 +1378,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="19.375" customWidth="1"/>
@@ -2187,6 +2223,206 @@
         <v>19</v>
       </c>
     </row>
+    <row r="46" spans="1:7">
+      <c r="A46" t="s">
+        <v>56</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" t="s">
+        <v>58</v>
+      </c>
+      <c r="D46">
+        <v>20</v>
+      </c>
+      <c r="E46">
+        <v>2</v>
+      </c>
+      <c r="F46">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" t="s">
+        <v>56</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C47" t="s">
+        <v>59</v>
+      </c>
+      <c r="D47">
+        <v>15</v>
+      </c>
+      <c r="E47">
+        <v>5</v>
+      </c>
+      <c r="F47">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" t="s">
+        <v>56</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" t="s">
+        <v>60</v>
+      </c>
+      <c r="D48">
+        <v>15</v>
+      </c>
+      <c r="E48">
+        <v>5</v>
+      </c>
+      <c r="F48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49" t="s">
+        <v>61</v>
+      </c>
+      <c r="D49">
+        <v>20</v>
+      </c>
+      <c r="E49">
+        <v>1</v>
+      </c>
+      <c r="F49">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C50" t="s">
+        <v>62</v>
+      </c>
+      <c r="D50">
+        <v>20</v>
+      </c>
+      <c r="E50">
+        <v>5</v>
+      </c>
+      <c r="F50">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C51" t="s">
+        <v>63</v>
+      </c>
+      <c r="D51">
+        <v>15</v>
+      </c>
+      <c r="E51">
+        <v>4</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" t="s">
+        <v>56</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C52" t="s">
+        <v>64</v>
+      </c>
+      <c r="D52">
+        <v>20</v>
+      </c>
+      <c r="E52">
+        <v>2</v>
+      </c>
+      <c r="F52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" t="s">
+        <v>56</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C53" t="s">
+        <v>65</v>
+      </c>
+      <c r="D53">
+        <v>15</v>
+      </c>
+      <c r="E53">
+        <v>5</v>
+      </c>
+      <c r="F53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C54" t="s">
+        <v>66</v>
+      </c>
+      <c r="D54">
+        <v>25</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" t="s">
+        <v>56</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C55" t="s">
+        <v>67</v>
+      </c>
+      <c r="D55">
+        <v>10</v>
+      </c>
+      <c r="E55">
+        <v>10</v>
+      </c>
+      <c r="F55">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
